--- a/diseases/d184/2026-2029.xlsx
+++ b/diseases/d184/2026-2029.xlsx
@@ -1639,13 +1639,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>26801</v>
+        <v>31413</v>
       </c>
       <c r="O8" t="n">
-        <v>26801</v>
+        <v>31413</v>
       </c>
       <c r="R8" t="n">
-        <v>12.54947807087809</v>
+        <v>14.70903155257242</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1784,13 +1784,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2970</v>
+        <v>29824</v>
       </c>
       <c r="O9" t="n">
-        <v>2970</v>
+        <v>29824</v>
       </c>
       <c r="R9" t="n">
-        <v>1.390692506641839</v>
+        <v>13.96498764918727</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1857,6 +1857,151 @@
         </is>
       </c>
       <c r="BC9" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>D184</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>accident-caused-by-venomous-animals</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Accident caused by venomous animals</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>D184</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Accident caused by venomous animals</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>毒性动物伤害</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>1082</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1082</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.5066428593220436</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>ftp_dbc</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>sinan_datasus</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>Brazil DATASUS SINAN</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>http://siab.datasus.gov.br/DATASUS/index.php?acao=41&amp;area=0901&amp;item=1</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
         <is>
           <t>ftp_dbc</t>
         </is>
@@ -1895,7 +2040,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -1978,7 +2123,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -1988,7 +2133,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
@@ -2040,7 +2185,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>231045</v>
+        <v>263593</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d184/2026-2029.xlsx
+++ b/diseases/d184/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1057,6 +1067,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1193,6 +1208,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1329,6 +1349,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1465,6 +1490,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1601,6 +1631,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1737,6 +1772,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1873,6 +1913,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2009,6 +2054,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2145,6 +2195,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2281,6 +2336,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2417,6 +2477,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2553,6 +2618,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2689,6 +2759,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2825,6 +2900,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2961,6 +3041,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3097,6 +3182,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3233,6 +3323,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3369,6 +3464,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3505,6 +3605,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3641,6 +3746,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3777,6 +3887,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3913,6 +4028,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4049,6 +4169,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4185,6 +4310,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4321,6 +4451,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4457,6 +4592,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4596,6 +4736,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4741,6 +4886,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4877,6 +5027,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5013,6 +5168,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5149,6 +5309,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5285,6 +5450,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5421,6 +5591,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5557,6 +5732,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5693,6 +5873,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5829,6 +6014,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5965,6 +6155,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6101,6 +6296,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6237,6 +6437,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6373,6 +6578,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6509,6 +6719,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6645,6 +6860,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6781,6 +7001,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6917,6 +7142,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7053,6 +7283,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7189,6 +7424,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7325,6 +7565,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7461,6 +7706,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7597,6 +7847,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7733,6 +7988,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7869,6 +8129,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8005,6 +8270,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8141,6 +8411,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8277,6 +8552,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8416,6 +8696,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8561,6 +8846,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8697,6 +8987,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8833,6 +9128,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8969,6 +9269,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9105,6 +9410,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9241,6 +9551,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9377,6 +9692,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9513,6 +9833,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9649,6 +9974,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9785,6 +10115,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9921,6 +10256,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10057,6 +10397,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10193,6 +10538,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10329,6 +10679,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10465,6 +10820,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10601,6 +10961,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10737,6 +11102,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10873,6 +11243,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11009,6 +11384,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11145,6 +11525,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11281,6 +11666,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11417,6 +11807,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11553,6 +11948,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11689,6 +12089,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11825,6 +12230,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11961,6 +12371,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12097,6 +12512,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12233,6 +12653,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12378,6 +12803,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12514,6 +12944,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12650,6 +13085,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12786,6 +13226,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12922,6 +13367,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13058,6 +13508,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13194,6 +13649,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13330,6 +13790,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13466,6 +13931,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13602,6 +14072,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13738,6 +14213,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13874,6 +14354,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14010,6 +14495,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14146,6 +14636,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14282,6 +14777,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14418,6 +14918,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14554,6 +15059,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14690,6 +15200,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14826,6 +15341,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14962,6 +15482,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15098,6 +15623,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15234,6 +15764,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15370,6 +15905,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15506,6 +16046,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15642,6 +16187,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15778,6 +16328,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15914,6 +16469,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16050,6 +16610,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16195,6 +16760,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16331,6 +16901,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16467,6 +17042,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16603,6 +17183,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16739,6 +17324,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16875,6 +17465,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17011,6 +17606,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17147,6 +17747,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17283,6 +17888,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17419,6 +18029,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17555,6 +18170,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17691,6 +18311,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17827,6 +18452,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17963,6 +18593,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18099,6 +18734,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18235,6 +18875,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18371,6 +19016,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18507,6 +19157,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18643,6 +19298,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18779,6 +19439,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18915,6 +19580,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19051,6 +19721,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19187,6 +19862,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19323,6 +20003,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19459,6 +20144,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19595,6 +20285,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19731,6 +20426,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19867,6 +20567,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20012,6 +20717,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20148,6 +20858,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20284,6 +20999,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20420,6 +21140,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20556,6 +21281,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20692,6 +21422,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20828,6 +21563,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20964,6 +21704,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21100,6 +21845,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21236,6 +21986,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21372,6 +22127,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO153" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21508,6 +22268,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21644,6 +22409,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21780,6 +22550,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21916,6 +22691,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22052,6 +22832,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22188,6 +22973,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22324,6 +23114,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22460,6 +23255,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22596,6 +23396,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22732,6 +23537,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22868,6 +23678,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23004,6 +23819,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23140,6 +23960,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23276,6 +24101,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23412,6 +24242,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23548,6 +24383,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23684,6 +24524,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23829,6 +24674,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23965,6 +24815,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24101,6 +24956,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24237,6 +25097,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24373,6 +25238,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24509,6 +25379,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO176" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24645,6 +25520,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO177" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24781,6 +25661,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO178" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24917,6 +25802,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO179" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25053,6 +25943,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25189,6 +26084,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO181" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25325,6 +26225,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO182" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25461,6 +26366,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO183" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25597,6 +26507,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25733,6 +26648,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO185" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25869,6 +26789,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26005,6 +26930,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO187" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26141,6 +27071,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26277,6 +27212,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO189" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26413,6 +27353,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO190" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26549,6 +27494,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO191" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26685,6 +27635,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26821,6 +27776,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26957,6 +27917,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27093,6 +28058,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27229,6 +28199,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27365,6 +28340,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27501,6 +28481,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO198" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27646,6 +28631,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO199" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27782,6 +28772,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27918,6 +28913,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO201" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28054,6 +29054,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO202" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28190,6 +29195,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO203" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28326,6 +29336,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28462,6 +29477,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO205" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28598,6 +29618,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO206" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28734,6 +29759,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28870,6 +29900,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO208" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29006,6 +30041,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO209" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29142,6 +30182,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO210" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29278,6 +30323,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO211" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29414,6 +30464,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO212" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29550,6 +30605,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO213" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29686,6 +30746,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO214" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29822,6 +30887,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO215" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29958,6 +31028,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO216" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30094,6 +31169,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO217" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30230,6 +31310,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO218" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30366,6 +31451,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO219" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30502,6 +31592,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO220" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30638,6 +31733,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO221" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30774,6 +31874,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO222" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30910,6 +32015,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO223" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31046,6 +32156,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO224" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31182,6 +32297,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO225" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31318,6 +32438,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO226" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31463,6 +32588,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO227" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31599,6 +32729,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO228" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31735,6 +32870,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO229" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31871,6 +33011,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO230" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32007,6 +33152,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO231" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32143,6 +33293,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO232" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32279,6 +33434,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO233" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32415,6 +33575,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO234" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32551,6 +33716,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO235" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32687,6 +33857,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO236" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32823,6 +33998,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO237" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32959,6 +34139,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO238" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33095,6 +34280,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO239" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33231,6 +34421,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO240" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33367,6 +34562,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO241" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33503,6 +34703,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO242" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33639,6 +34844,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO243" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33775,6 +34985,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO244" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33911,6 +35126,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO245" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34047,6 +35267,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO246" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34183,6 +35408,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO247" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34319,6 +35549,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO248" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34455,6 +35690,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO249" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34591,6 +35831,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO250" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34727,6 +35972,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO251" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34863,6 +36113,11 @@
           <t>ibge_computed</t>
         </is>
       </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO252" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34997,6 +36252,11 @@
       <c r="S253" t="inlineStr">
         <is>
           <t>ibge_computed</t>
+        </is>
+      </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO253" t="inlineStr">

--- a/diseases/d184/2026-2029.xlsx
+++ b/diseases/d184/2026-2029.xlsx
@@ -771,11 +771,6 @@
       <c r="R2" t="n">
         <v>17.62646753541776</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -788,23 +783,13 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
@@ -921,11 +906,6 @@
       <c r="R3" t="n">
         <v>15.09359153136876</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -938,23 +918,13 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
       </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV3" t="inlineStr">
         <is>
           <t>all</t>
@@ -1062,11 +1032,6 @@
       <c r="R4" t="n">
         <v>48.43023934472644</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1079,23 +1044,13 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV4" t="inlineStr">
         <is>
           <t>all</t>
@@ -1203,11 +1158,6 @@
       <c r="R5" t="n">
         <v>9.585120224466088</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1220,23 +1170,13 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV5" t="inlineStr">
         <is>
           <t>all</t>
@@ -1344,11 +1284,6 @@
       <c r="R6" t="n">
         <v>13.08717913261634</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1361,23 +1296,13 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
       </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV6" t="inlineStr">
         <is>
           <t>all</t>
@@ -1485,11 +1410,6 @@
       <c r="R7" t="n">
         <v>25.48780776108111</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1502,23 +1422,13 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
       </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV7" t="inlineStr">
         <is>
           <t>all</t>
@@ -1626,11 +1536,6 @@
       <c r="R8" t="n">
         <v>13.28716366463844</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1643,23 +1548,13 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
       </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV8" t="inlineStr">
         <is>
           <t>all</t>
@@ -1767,11 +1662,6 @@
       <c r="R9" t="n">
         <v>17.74088736330547</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1784,23 +1674,13 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
       </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV9" t="inlineStr">
         <is>
           <t>all</t>
@@ -1908,11 +1788,6 @@
       <c r="R10" t="n">
         <v>17.61152116321809</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1925,23 +1800,13 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
       </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV10" t="inlineStr">
         <is>
           <t>all</t>
@@ -2049,11 +1914,6 @@
       <c r="R11" t="n">
         <v>18.13200822464691</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2066,23 +1926,13 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
       </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV11" t="inlineStr">
         <is>
           <t>all</t>
@@ -2190,11 +2040,6 @@
       <c r="R12" t="n">
         <v>9.765740387614478</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2207,23 +2052,13 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
       </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV12" t="inlineStr">
         <is>
           <t>all</t>
@@ -2331,11 +2166,6 @@
       <c r="R13" t="n">
         <v>26.83092523682439</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2348,23 +2178,13 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
       </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV13" t="inlineStr">
         <is>
           <t>all</t>
@@ -2472,11 +2292,6 @@
       <c r="R14" t="n">
         <v>33.6691537264999</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2489,23 +2304,13 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
       </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV14" t="inlineStr">
         <is>
           <t>all</t>
@@ -2613,11 +2418,6 @@
       <c r="R15" t="n">
         <v>9.062534016145486</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2630,23 +2430,13 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
       </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV15" t="inlineStr">
         <is>
           <t>all</t>
@@ -2754,11 +2544,6 @@
       <c r="R16" t="n">
         <v>13.39603239898386</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2771,23 +2556,13 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
       </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV16" t="inlineStr">
         <is>
           <t>all</t>
@@ -2895,11 +2670,6 @@
       <c r="R17" t="n">
         <v>24.28978671845938</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2912,23 +2682,13 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
       </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV17" t="inlineStr">
         <is>
           <t>all</t>
@@ -3036,11 +2796,6 @@
       <c r="R18" t="n">
         <v>24.0316988856304</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3053,23 +2808,13 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
       </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV18" t="inlineStr">
         <is>
           <t>all</t>
@@ -3177,11 +2922,6 @@
       <c r="R19" t="n">
         <v>23.34481021583044</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3194,23 +2934,13 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
       </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV19" t="inlineStr">
         <is>
           <t>all</t>
@@ -3318,11 +3048,6 @@
       <c r="R20" t="n">
         <v>22.48910182141645</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3335,23 +3060,13 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
       </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV20" t="inlineStr">
         <is>
           <t>all</t>
@@ -3459,11 +3174,6 @@
       <c r="R21" t="n">
         <v>2.850440134661526</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3476,23 +3186,13 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
       </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV21" t="inlineStr">
         <is>
           <t>all</t>
@@ -3600,11 +3300,6 @@
       <c r="R22" t="n">
         <v>22.63451295522726</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3617,23 +3312,13 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
       </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV22" t="inlineStr">
         <is>
           <t>all</t>
@@ -3741,11 +3426,6 @@
       <c r="R23" t="n">
         <v>10.24276490919789</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3758,23 +3438,13 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
       </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV23" t="inlineStr">
         <is>
           <t>all</t>
@@ -3882,11 +3552,6 @@
       <c r="R24" t="n">
         <v>15.11145684956348</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3899,23 +3564,13 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
       </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV24" t="inlineStr">
         <is>
           <t>all</t>
@@ -4023,11 +3678,6 @@
       <c r="R25" t="n">
         <v>14.10981280061802</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4040,23 +3690,13 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
       </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV25" t="inlineStr">
         <is>
           <t>all</t>
@@ -4164,11 +3804,6 @@
       <c r="R26" t="n">
         <v>15.39801647082515</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4181,23 +3816,13 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
       </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV26" t="inlineStr">
         <is>
           <t>all</t>
@@ -4305,11 +3930,6 @@
       <c r="R27" t="n">
         <v>19.24364667104416</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4322,23 +3942,13 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
       </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV27" t="inlineStr">
         <is>
           <t>all</t>
@@ -4446,11 +4056,6 @@
       <c r="R28" t="n">
         <v>16.12420951095355</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4463,23 +4068,13 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
       </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV28" t="inlineStr">
         <is>
           <t>all</t>
@@ -4587,11 +4182,6 @@
       <c r="R29" t="n">
         <v>37.40615566223934</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4604,23 +4194,13 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
       </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV29" t="inlineStr">
         <is>
           <t>all</t>
@@ -4731,11 +4311,6 @@
       <c r="R30" t="n">
         <v>15.8296490189756</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4748,23 +4323,13 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
       </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV30" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
@@ -4881,11 +4446,6 @@
       <c r="R31" t="n">
         <v>14.1924815891975</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4898,23 +4458,13 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
       </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV31" t="inlineStr">
         <is>
           <t>all</t>
@@ -5022,11 +4572,6 @@
       <c r="R32" t="n">
         <v>43.64930546069576</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5039,23 +4584,13 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
       </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV32" t="inlineStr">
         <is>
           <t>all</t>
@@ -5163,11 +4698,6 @@
       <c r="R33" t="n">
         <v>9.241156580047448</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5180,23 +4710,13 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
       </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV33" t="inlineStr">
         <is>
           <t>all</t>
@@ -5304,11 +4824,6 @@
       <c r="R34" t="n">
         <v>11.85253959180347</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5321,23 +4836,13 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
       </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV34" t="inlineStr">
         <is>
           <t>all</t>
@@ -5445,11 +4950,6 @@
       <c r="R35" t="n">
         <v>21.1088747807847</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5462,23 +4962,13 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
       </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV35" t="inlineStr">
         <is>
           <t>all</t>
@@ -5586,11 +5076,6 @@
       <c r="R36" t="n">
         <v>14.58792968682392</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5603,23 +5088,13 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
       </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV36" t="inlineStr">
         <is>
           <t>all</t>
@@ -5727,11 +5202,6 @@
       <c r="R37" t="n">
         <v>14.1528427280302</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5744,23 +5214,13 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
       </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV37" t="inlineStr">
         <is>
           <t>all</t>
@@ -5868,11 +5328,6 @@
       <c r="R38" t="n">
         <v>13.82901935388123</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5885,23 +5340,13 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
       </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV38" t="inlineStr">
         <is>
           <t>all</t>
@@ -6009,11 +5454,6 @@
       <c r="R39" t="n">
         <v>15.62368037605705</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6026,23 +5466,13 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
       </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV39" t="inlineStr">
         <is>
           <t>all</t>
@@ -6150,11 +5580,6 @@
       <c r="R40" t="n">
         <v>7.673081733125662</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6167,23 +5592,13 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
       </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV40" t="inlineStr">
         <is>
           <t>all</t>
@@ -6291,11 +5706,6 @@
       <c r="R41" t="n">
         <v>25.88033323468611</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6308,23 +5718,13 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
       </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV41" t="inlineStr">
         <is>
           <t>all</t>
@@ -6432,11 +5832,6 @@
       <c r="R42" t="n">
         <v>28.95139932329074</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6449,23 +5844,13 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
       </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV42" t="inlineStr">
         <is>
           <t>all</t>
@@ -6573,11 +5958,6 @@
       <c r="R43" t="n">
         <v>8.632190222082711</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6590,23 +5970,13 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
       </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV43" t="inlineStr">
         <is>
           <t>all</t>
@@ -6714,11 +6084,6 @@
       <c r="R44" t="n">
         <v>12.49382731840439</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6731,23 +6096,13 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
       </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV44" t="inlineStr">
         <is>
           <t>all</t>
@@ -6855,11 +6210,6 @@
       <c r="R45" t="n">
         <v>23.93117766257661</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6872,23 +6222,13 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
       </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV45" t="inlineStr">
         <is>
           <t>all</t>
@@ -6996,11 +6336,6 @@
       <c r="R46" t="n">
         <v>23.16559770998675</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7013,23 +6348,13 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
       </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV46" t="inlineStr">
         <is>
           <t>all</t>
@@ -7137,11 +6462,6 @@
       <c r="R47" t="n">
         <v>19.68981467698829</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7154,23 +6474,13 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
       </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV47" t="inlineStr">
         <is>
           <t>all</t>
@@ -7278,11 +6588,6 @@
       <c r="R48" t="n">
         <v>20.47277982031476</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7295,23 +6600,13 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
       </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV48" t="inlineStr">
         <is>
           <t>all</t>
@@ -7419,11 +6714,6 @@
       <c r="R49" t="n">
         <v>2.513728265393973</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7436,23 +6726,13 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
       </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV49" t="inlineStr">
         <is>
           <t>all</t>
@@ -7560,11 +6840,6 @@
       <c r="R50" t="n">
         <v>22.51903074627202</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7577,23 +6852,13 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
       </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV50" t="inlineStr">
         <is>
           <t>all</t>
@@ -7701,11 +6966,6 @@
       <c r="R51" t="n">
         <v>6.600892941483084</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7718,23 +6978,13 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
       </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV51" t="inlineStr">
         <is>
           <t>all</t>
@@ -7842,11 +7092,6 @@
       <c r="R52" t="n">
         <v>13.53460917830468</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7859,23 +7104,13 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
       </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV52" t="inlineStr">
         <is>
           <t>all</t>
@@ -7983,11 +7218,6 @@
       <c r="R53" t="n">
         <v>11.78636728581593</v>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8000,23 +7230,13 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
       </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV53" t="inlineStr">
         <is>
           <t>all</t>
@@ -8124,11 +7344,6 @@
       <c r="R54" t="n">
         <v>12.79960119137341</v>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8141,23 +7356,13 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
       </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV54" t="inlineStr">
         <is>
           <t>all</t>
@@ -8265,11 +7470,6 @@
       <c r="R55" t="n">
         <v>19.28698821760057</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8282,23 +7482,13 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
       </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV55" t="inlineStr">
         <is>
           <t>all</t>
@@ -8406,11 +7596,6 @@
       <c r="R56" t="n">
         <v>15.32297965343907</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8423,23 +7608,13 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
       </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV56" t="inlineStr">
         <is>
           <t>all</t>
@@ -8547,11 +7722,6 @@
       <c r="R57" t="n">
         <v>33.33345864708765</v>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8564,23 +7734,13 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
       </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV57" t="inlineStr">
         <is>
           <t>all</t>
@@ -8691,11 +7851,6 @@
       <c r="R58" t="n">
         <v>16.54949681122133</v>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8708,23 +7863,13 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
       </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV58" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
@@ -8841,11 +7986,6 @@
       <c r="R59" t="n">
         <v>13.51664913256904</v>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8858,23 +7998,13 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
       </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV59" t="inlineStr">
         <is>
           <t>all</t>
@@ -8982,11 +8112,6 @@
       <c r="R60" t="n">
         <v>54.14252398538648</v>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8999,23 +8124,13 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
       </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV60" t="inlineStr">
         <is>
           <t>all</t>
@@ -9123,11 +8238,6 @@
       <c r="R61" t="n">
         <v>10.73166570586155</v>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9140,23 +8250,13 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
       </c>
-      <c r="AU61" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV61" t="inlineStr">
         <is>
           <t>all</t>
@@ -9264,11 +8364,6 @@
       <c r="R62" t="n">
         <v>12.59332331629119</v>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9281,23 +8376,13 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR62" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
       </c>
-      <c r="AU62" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV62" t="inlineStr">
         <is>
           <t>all</t>
@@ -9405,11 +8490,6 @@
       <c r="R63" t="n">
         <v>25.42736236718132</v>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9422,23 +8502,13 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
       </c>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV63" t="inlineStr">
         <is>
           <t>all</t>
@@ -9546,11 +8616,6 @@
       <c r="R64" t="n">
         <v>13.97517213918282</v>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9563,23 +8628,13 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR64" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
       </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV64" t="inlineStr">
         <is>
           <t>all</t>
@@ -9687,11 +8742,6 @@
       <c r="R65" t="n">
         <v>15.21596706440806</v>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9704,23 +8754,13 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
       </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV65" t="inlineStr">
         <is>
           <t>all</t>
@@ -9828,11 +8868,6 @@
       <c r="R66" t="n">
         <v>17.27422800824537</v>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9845,23 +8880,13 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR66" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
       </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV66" t="inlineStr">
         <is>
           <t>all</t>
@@ -9969,11 +8994,6 @@
       <c r="R67" t="n">
         <v>17.74508531183252</v>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -9986,23 +9006,13 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR67" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
       </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV67" t="inlineStr">
         <is>
           <t>all</t>
@@ -10110,11 +9120,6 @@
       <c r="R68" t="n">
         <v>9.039715956465297</v>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10127,23 +9132,13 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR68" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
       </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV68" t="inlineStr">
         <is>
           <t>all</t>
@@ -10251,11 +9246,6 @@
       <c r="R69" t="n">
         <v>28.69483112337002</v>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10268,23 +9258,13 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR69" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
       </c>
-      <c r="AU69" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV69" t="inlineStr">
         <is>
           <t>all</t>
@@ -10392,11 +9372,6 @@
       <c r="R70" t="n">
         <v>28.95139932329074</v>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10409,23 +9384,13 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
       </c>
-      <c r="AU70" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV70" t="inlineStr">
         <is>
           <t>all</t>
@@ -10533,11 +9498,6 @@
       <c r="R71" t="n">
         <v>9.113162697799931</v>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10550,23 +9510,13 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR71" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="n">
         <v>0</v>
       </c>
-      <c r="AU71" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV71" t="inlineStr">
         <is>
           <t>all</t>
@@ -10674,11 +9624,6 @@
       <c r="R72" t="n">
         <v>13.65869970092472</v>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10691,23 +9636,13 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR72" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
         <v>0</v>
       </c>
-      <c r="AU72" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV72" t="inlineStr">
         <is>
           <t>all</t>
@@ -10815,11 +9750,6 @@
       <c r="R73" t="n">
         <v>31.36633875454597</v>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10832,23 +9762,13 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR73" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="n">
         <v>0</v>
       </c>
-      <c r="AU73" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV73" t="inlineStr">
         <is>
           <t>all</t>
@@ -10956,11 +9876,6 @@
       <c r="R74" t="n">
         <v>28.47698925700624</v>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -10973,23 +9888,13 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR74" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
         <v>0</v>
       </c>
-      <c r="AU74" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV74" t="inlineStr">
         <is>
           <t>all</t>
@@ -11097,11 +10002,6 @@
       <c r="R75" t="n">
         <v>21.25203051213856</v>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11114,23 +10014,13 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR75" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
         <v>0</v>
       </c>
-      <c r="AU75" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV75" t="inlineStr">
         <is>
           <t>all</t>
@@ -11238,11 +10128,6 @@
       <c r="R76" t="n">
         <v>21.52695646819365</v>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11255,23 +10140,13 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="n">
         <v>0</v>
       </c>
-      <c r="AU76" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV76" t="inlineStr">
         <is>
           <t>all</t>
@@ -11379,11 +10254,6 @@
       <c r="R77" t="n">
         <v>2.653057314746064</v>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11396,23 +10266,13 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR77" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="n">
         <v>0</v>
       </c>
-      <c r="AU77" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV77" t="inlineStr">
         <is>
           <t>all</t>
@@ -11520,11 +10380,6 @@
       <c r="R78" t="n">
         <v>26.30107308955616</v>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11537,23 +10392,13 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR78" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
         <v>0</v>
       </c>
-      <c r="AU78" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV78" t="inlineStr">
         <is>
           <t>all</t>
@@ -11661,11 +10506,6 @@
       <c r="R79" t="n">
         <v>10.07205216071126</v>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11678,23 +10518,13 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR79" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
         <v>0</v>
       </c>
-      <c r="AU79" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV79" t="inlineStr">
         <is>
           <t>all</t>
@@ -11802,11 +10632,6 @@
       <c r="R80" t="n">
         <v>12.87758931528018</v>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11819,23 +10644,13 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR80" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
         <v>0</v>
       </c>
-      <c r="AU80" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV80" t="inlineStr">
         <is>
           <t>all</t>
@@ -11943,11 +10758,6 @@
       <c r="R81" t="n">
         <v>11.8397798263861</v>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -11960,23 +10770,13 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR81" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
         <v>0</v>
       </c>
-      <c r="AU81" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV81" t="inlineStr">
         <is>
           <t>all</t>
@@ -12084,11 +10884,6 @@
       <c r="R82" t="n">
         <v>13.60559111601816</v>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12101,23 +10896,13 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR82" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="n">
         <v>0</v>
       </c>
-      <c r="AU82" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV82" t="inlineStr">
         <is>
           <t>all</t>
@@ -12225,11 +11010,6 @@
       <c r="R83" t="n">
         <v>22.71097039555663</v>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12242,23 +11022,13 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR83" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
         <v>0</v>
       </c>
-      <c r="AU83" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV83" t="inlineStr">
         <is>
           <t>all</t>
@@ -12366,11 +11136,6 @@
       <c r="R84" t="n">
         <v>15.43775041681277</v>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12383,23 +11148,13 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR84" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
         <v>0</v>
       </c>
-      <c r="AU84" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV84" t="inlineStr">
         <is>
           <t>all</t>
@@ -12507,11 +11262,6 @@
       <c r="R85" t="n">
         <v>32.08032110396405</v>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12524,23 +11274,13 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR85" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
         <v>0</v>
       </c>
-      <c r="AU85" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV85" t="inlineStr">
         <is>
           <t>all</t>
@@ -12648,11 +11388,6 @@
       <c r="R86" t="n">
         <v>16.16716520172117</v>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12665,23 +11400,13 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR86" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
         <v>0</v>
       </c>
-      <c r="AU86" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV86" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
@@ -12798,11 +11523,6 @@
       <c r="R87" t="n">
         <v>11.26387427714087</v>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12815,23 +11535,13 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR87" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
         <v>0</v>
       </c>
-      <c r="AU87" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV87" t="inlineStr">
         <is>
           <t>all</t>
@@ -12939,11 +11649,6 @@
       <c r="R88" t="n">
         <v>53.64580358185083</v>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -12956,23 +11661,13 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR88" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="n">
         <v>0</v>
       </c>
-      <c r="AU88" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV88" t="inlineStr">
         <is>
           <t>all</t>
@@ -13080,11 +11775,6 @@
       <c r="R89" t="n">
         <v>8.920123845256718</v>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13097,23 +11787,13 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR89" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="n">
         <v>0</v>
       </c>
-      <c r="AU89" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV89" t="inlineStr">
         <is>
           <t>all</t>
@@ -13221,11 +11901,6 @@
       <c r="R90" t="n">
         <v>13.82796285710405</v>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13238,23 +11913,13 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR90" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
         <v>0</v>
       </c>
-      <c r="AU90" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV90" t="inlineStr">
         <is>
           <t>all</t>
@@ -13362,11 +12027,6 @@
       <c r="R91" t="n">
         <v>23.10357277947801</v>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13379,23 +12039,13 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR91" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="n">
         <v>0</v>
       </c>
-      <c r="AU91" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV91" t="inlineStr">
         <is>
           <t>all</t>
@@ -13503,11 +12153,6 @@
       <c r="R92" t="n">
         <v>13.94292174193856</v>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13520,23 +12165,13 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="n">
         <v>0</v>
       </c>
-      <c r="AU92" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV92" t="inlineStr">
         <is>
           <t>all</t>
@@ -13644,11 +12279,6 @@
       <c r="R93" t="n">
         <v>16.41198194283314</v>
       </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13661,23 +12291,13 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR93" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="n">
         <v>0</v>
       </c>
-      <c r="AU93" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV93" t="inlineStr">
         <is>
           <t>all</t>
@@ -13785,11 +12405,6 @@
       <c r="R94" t="n">
         <v>17.41878221751939</v>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13802,23 +12417,13 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR94" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="n">
         <v>0</v>
       </c>
-      <c r="AU94" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV94" t="inlineStr">
         <is>
           <t>all</t>
@@ -13926,11 +12531,6 @@
       <c r="R95" t="n">
         <v>18.25208774931345</v>
       </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -13943,23 +12543,13 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR95" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="n">
         <v>0</v>
       </c>
-      <c r="AU95" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV95" t="inlineStr">
         <is>
           <t>all</t>
@@ -14067,11 +12657,6 @@
       <c r="R96" t="n">
         <v>8.014740288960571</v>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14084,23 +12669,13 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR96" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="n">
         <v>0</v>
       </c>
-      <c r="AU96" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV96" t="inlineStr">
         <is>
           <t>all</t>
@@ -14208,11 +12783,6 @@
       <c r="R97" t="n">
         <v>27.56716806200991</v>
       </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14225,23 +12795,13 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR97" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="n">
         <v>0</v>
       </c>
-      <c r="AU97" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV97" t="inlineStr">
         <is>
           <t>all</t>
@@ -14349,11 +12909,6 @@
       <c r="R98" t="n">
         <v>22.53661096209267</v>
       </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14366,23 +12921,13 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR98" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="n">
         <v>0</v>
       </c>
-      <c r="AU98" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV98" t="inlineStr">
         <is>
           <t>all</t>
@@ -14490,11 +13035,6 @@
       <c r="R99" t="n">
         <v>8.708133244564378</v>
       </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14507,23 +13047,13 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR99" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="n">
         <v>0</v>
       </c>
-      <c r="AU99" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV99" t="inlineStr">
         <is>
           <t>all</t>
@@ -14631,11 +13161,6 @@
       <c r="R100" t="n">
         <v>13.13336509704301</v>
       </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14648,23 +13173,13 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR100" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="n">
         <v>0</v>
       </c>
-      <c r="AU100" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV100" t="inlineStr">
         <is>
           <t>all</t>
@@ -14772,11 +13287,6 @@
       <c r="R101" t="n">
         <v>30.95991515787884</v>
       </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14789,23 +13299,13 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR101" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="n">
         <v>0</v>
       </c>
-      <c r="AU101" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV101" t="inlineStr">
         <is>
           <t>all</t>
@@ -14913,11 +13413,6 @@
       <c r="R102" t="n">
         <v>29.15526126202837</v>
       </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -14930,23 +13425,13 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR102" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr"/>
       <c r="AT102" t="n">
         <v>0</v>
       </c>
-      <c r="AU102" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV102" t="inlineStr">
         <is>
           <t>all</t>
@@ -15054,11 +13539,6 @@
       <c r="R103" t="n">
         <v>20.2203785455299</v>
       </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15071,23 +13551,13 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR103" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr"/>
       <c r="AT103" t="n">
         <v>0</v>
       </c>
-      <c r="AU103" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV103" t="inlineStr">
         <is>
           <t>all</t>
@@ -15195,11 +13665,6 @@
       <c r="R104" t="n">
         <v>17.24331802601909</v>
       </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15212,23 +13677,13 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR104" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr"/>
       <c r="AT104" t="n">
         <v>0</v>
       </c>
-      <c r="AU104" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV104" t="inlineStr">
         <is>
           <t>all</t>
@@ -15336,11 +13791,6 @@
       <c r="R105" t="n">
         <v>2.658862691802401</v>
       </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15353,23 +13803,13 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR105" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr"/>
       <c r="AT105" t="n">
         <v>0</v>
       </c>
-      <c r="AU105" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV105" t="inlineStr">
         <is>
           <t>all</t>
@@ -15477,11 +13917,6 @@
       <c r="R106" t="n">
         <v>24.77093382089922</v>
       </c>
-      <c r="S106" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15494,23 +13929,13 @@
       </c>
       <c r="AP106" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR106" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS106" t="inlineStr"/>
       <c r="AT106" t="n">
         <v>0</v>
       </c>
-      <c r="AU106" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV106" t="inlineStr">
         <is>
           <t>all</t>
@@ -15618,11 +14043,6 @@
       <c r="R107" t="n">
         <v>8.990871420295925</v>
       </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15635,23 +14055,13 @@
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR107" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr"/>
       <c r="AT107" t="n">
         <v>0</v>
       </c>
-      <c r="AU107" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV107" t="inlineStr">
         <is>
           <t>all</t>
@@ -15759,11 +14169,6 @@
       <c r="R108" t="n">
         <v>13.66601315090958</v>
       </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15776,23 +14181,13 @@
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR108" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr"/>
       <c r="AT108" t="n">
         <v>0</v>
       </c>
-      <c r="AU108" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV108" t="inlineStr">
         <is>
           <t>all</t>
@@ -15900,11 +14295,6 @@
       <c r="R109" t="n">
         <v>9.454019680918824</v>
       </c>
-      <c r="S109" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -15917,23 +14307,13 @@
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR109" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr"/>
       <c r="AT109" t="n">
         <v>0</v>
       </c>
-      <c r="AU109" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV109" t="inlineStr">
         <is>
           <t>all</t>
@@ -16041,11 +14421,6 @@
       <c r="R110" t="n">
         <v>11.47633415091187</v>
       </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16058,23 +14433,13 @@
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR110" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr"/>
       <c r="AT110" t="n">
         <v>0</v>
       </c>
-      <c r="AU110" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV110" t="inlineStr">
         <is>
           <t>all</t>
@@ -16182,11 +14547,6 @@
       <c r="R111" t="n">
         <v>20.71725925396196</v>
       </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16199,23 +14559,13 @@
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR111" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr"/>
       <c r="AT111" t="n">
         <v>0</v>
       </c>
-      <c r="AU111" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV111" t="inlineStr">
         <is>
           <t>all</t>
@@ -16323,11 +14673,6 @@
       <c r="R112" t="n">
         <v>15.59583090221427</v>
       </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16340,23 +14685,13 @@
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR112" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr"/>
       <c r="AT112" t="n">
         <v>0</v>
       </c>
-      <c r="AU112" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV112" t="inlineStr">
         <is>
           <t>all</t>
@@ -16464,11 +14799,6 @@
       <c r="R113" t="n">
         <v>31.39109545524607</v>
       </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16481,23 +14811,13 @@
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR113" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr"/>
       <c r="AT113" t="n">
         <v>0</v>
       </c>
-      <c r="AU113" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV113" t="inlineStr">
         <is>
           <t>all</t>
@@ -16605,11 +14925,6 @@
       <c r="R114" t="n">
         <v>14.94034289431405</v>
       </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16622,23 +14937,13 @@
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR114" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr"/>
       <c r="AT114" t="n">
         <v>0</v>
       </c>
-      <c r="AU114" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV114" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
@@ -16755,11 +15060,6 @@
       <c r="R115" t="n">
         <v>11.15123553436946</v>
       </c>
-      <c r="S115" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16772,23 +15072,13 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR115" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr"/>
       <c r="AT115" t="n">
         <v>0</v>
       </c>
-      <c r="AU115" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV115" t="inlineStr">
         <is>
           <t>all</t>
@@ -16896,11 +15186,6 @@
       <c r="R116" t="n">
         <v>54.57715433848018</v>
       </c>
-      <c r="S116" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -16913,23 +15198,13 @@
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR116" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr"/>
       <c r="AT116" t="n">
         <v>0</v>
       </c>
-      <c r="AU116" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV116" t="inlineStr">
         <is>
           <t>all</t>
@@ -17037,11 +15312,6 @@
       <c r="R117" t="n">
         <v>7.452545629070523</v>
       </c>
-      <c r="S117" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17054,23 +15324,13 @@
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR117" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr"/>
       <c r="AT117" t="n">
         <v>0</v>
       </c>
-      <c r="AU117" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV117" t="inlineStr">
         <is>
           <t>all</t>
@@ -17178,11 +15438,6 @@
       <c r="R118" t="n">
         <v>13.45757099486019</v>
       </c>
-      <c r="S118" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17195,23 +15450,13 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR118" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr"/>
       <c r="AT118" t="n">
         <v>0</v>
       </c>
-      <c r="AU118" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV118" t="inlineStr">
         <is>
           <t>all</t>
@@ -17319,11 +15564,6 @@
       <c r="R119" t="n">
         <v>24.46695221966232</v>
       </c>
-      <c r="S119" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17336,23 +15576,13 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR119" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr"/>
       <c r="AT119" t="n">
         <v>0</v>
       </c>
-      <c r="AU119" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV119" t="inlineStr">
         <is>
           <t>all</t>
@@ -17460,11 +15690,6 @@
       <c r="R120" t="n">
         <v>15.1791869696355</v>
       </c>
-      <c r="S120" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17477,23 +15702,13 @@
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR120" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr"/>
       <c r="AT120" t="n">
         <v>0</v>
       </c>
-      <c r="AU120" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV120" t="inlineStr">
         <is>
           <t>all</t>
@@ -17601,11 +15816,6 @@
       <c r="R121" t="n">
         <v>14.85051807377817</v>
       </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17618,23 +15828,13 @@
       </c>
       <c r="AP121" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR121" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS121" t="inlineStr"/>
       <c r="AT121" t="n">
         <v>0</v>
       </c>
-      <c r="AU121" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV121" t="inlineStr">
         <is>
           <t>all</t>
@@ -17742,11 +15942,6 @@
       <c r="R122" t="n">
         <v>18.69567773277323</v>
       </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17759,23 +15954,13 @@
       </c>
       <c r="AP122" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR122" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS122" t="inlineStr"/>
       <c r="AT122" t="n">
         <v>0</v>
       </c>
-      <c r="AU122" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV122" t="inlineStr">
         <is>
           <t>all</t>
@@ -17883,11 +16068,6 @@
       <c r="R123" t="n">
         <v>18.7057215091648</v>
       </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -17900,23 +16080,13 @@
       </c>
       <c r="AP123" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR123" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS123" t="inlineStr"/>
       <c r="AT123" t="n">
         <v>0</v>
       </c>
-      <c r="AU123" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV123" t="inlineStr">
         <is>
           <t>all</t>
@@ -18024,11 +16194,6 @@
       <c r="R124" t="n">
         <v>8.968537090666358</v>
       </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18041,23 +16206,13 @@
       </c>
       <c r="AP124" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR124" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS124" t="inlineStr"/>
       <c r="AT124" t="n">
         <v>0</v>
       </c>
-      <c r="AU124" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV124" t="inlineStr">
         <is>
           <t>all</t>
@@ -18165,11 +16320,6 @@
       <c r="R125" t="n">
         <v>26.11798123522068</v>
       </c>
-      <c r="S125" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18182,23 +16332,13 @@
       </c>
       <c r="AP125" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR125" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS125" t="inlineStr"/>
       <c r="AT125" t="n">
         <v>0</v>
       </c>
-      <c r="AU125" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV125" t="inlineStr">
         <is>
           <t>all</t>
@@ -18306,11 +16446,6 @@
       <c r="R126" t="n">
         <v>14.08538185130792</v>
       </c>
-      <c r="S126" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18323,23 +16458,13 @@
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR126" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr"/>
       <c r="AT126" t="n">
         <v>0</v>
       </c>
-      <c r="AU126" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV126" t="inlineStr">
         <is>
           <t>all</t>
@@ -18447,11 +16572,6 @@
       <c r="R127" t="n">
         <v>8.379046813810492</v>
       </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18464,23 +16584,13 @@
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR127" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr"/>
       <c r="AT127" t="n">
         <v>0</v>
       </c>
-      <c r="AU127" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV127" t="inlineStr">
         <is>
           <t>all</t>
@@ -18588,11 +16698,6 @@
       <c r="R128" t="n">
         <v>12.51666795335577</v>
       </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18605,23 +16710,13 @@
       </c>
       <c r="AP128" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR128" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS128" t="inlineStr"/>
       <c r="AT128" t="n">
         <v>0</v>
       </c>
-      <c r="AU128" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV128" t="inlineStr">
         <is>
           <t>all</t>
@@ -18729,11 +16824,6 @@
       <c r="R129" t="n">
         <v>32.53779500376301</v>
       </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18746,23 +16836,13 @@
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR129" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr"/>
       <c r="AT129" t="n">
         <v>0</v>
       </c>
-      <c r="AU129" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV129" t="inlineStr">
         <is>
           <t>all</t>
@@ -18870,11 +16950,6 @@
       <c r="R130" t="n">
         <v>30.2509314239872</v>
       </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA130" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -18887,23 +16962,13 @@
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR130" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr"/>
       <c r="AT130" t="n">
         <v>0</v>
       </c>
-      <c r="AU130" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV130" t="inlineStr">
         <is>
           <t>all</t>
@@ -19011,11 +17076,6 @@
       <c r="R131" t="n">
         <v>29.68210086785511</v>
       </c>
-      <c r="S131" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19028,23 +17088,13 @@
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR131" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr"/>
       <c r="AT131" t="n">
         <v>0</v>
       </c>
-      <c r="AU131" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV131" t="inlineStr">
         <is>
           <t>all</t>
@@ -19152,11 +17202,6 @@
       <c r="R132" t="n">
         <v>11.48717886934702</v>
       </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA132" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19169,23 +17214,13 @@
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR132" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS132" t="inlineStr"/>
       <c r="AT132" t="n">
         <v>0</v>
       </c>
-      <c r="AU132" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV132" t="inlineStr">
         <is>
           <t>all</t>
@@ -19293,11 +17328,6 @@
       <c r="R133" t="n">
         <v>2.502117511281299</v>
       </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19310,23 +17340,13 @@
       </c>
       <c r="AP133" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR133" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr"/>
       <c r="AT133" t="n">
         <v>0</v>
       </c>
-      <c r="AU133" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV133" t="inlineStr">
         <is>
           <t>all</t>
@@ -19434,11 +17454,6 @@
       <c r="R134" t="n">
         <v>23.35627676119752</v>
       </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19451,23 +17466,13 @@
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR134" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS134" t="inlineStr"/>
       <c r="AT134" t="n">
         <v>0</v>
       </c>
-      <c r="AU134" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV134" t="inlineStr">
         <is>
           <t>all</t>
@@ -19575,11 +17580,6 @@
       <c r="R135" t="n">
         <v>8.023499178871681</v>
       </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19592,23 +17592,13 @@
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR135" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS135" t="inlineStr"/>
       <c r="AT135" t="n">
         <v>0</v>
       </c>
-      <c r="AU135" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV135" t="inlineStr">
         <is>
           <t>all</t>
@@ -19716,11 +17706,6 @@
       <c r="R136" t="n">
         <v>13.40320520569978</v>
       </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19733,23 +17718,13 @@
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR136" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr"/>
       <c r="AT136" t="n">
         <v>0</v>
       </c>
-      <c r="AU136" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV136" t="inlineStr">
         <is>
           <t>all</t>
@@ -19857,11 +17832,6 @@
       <c r="R137" t="n">
         <v>5.528197949011854</v>
       </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -19874,23 +17844,13 @@
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR137" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr"/>
       <c r="AT137" t="n">
         <v>0</v>
       </c>
-      <c r="AU137" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV137" t="inlineStr">
         <is>
           <t>all</t>
@@ -19998,11 +17958,6 @@
       <c r="R138" t="n">
         <v>6.315592693111878</v>
       </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA138" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20015,23 +17970,13 @@
       </c>
       <c r="AP138" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR138" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS138" t="inlineStr"/>
       <c r="AT138" t="n">
         <v>0</v>
       </c>
-      <c r="AU138" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV138" t="inlineStr">
         <is>
           <t>all</t>
@@ -20139,11 +18084,6 @@
       <c r="R139" t="n">
         <v>18.68020656581089</v>
       </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20156,23 +18096,13 @@
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR139" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS139" t="inlineStr"/>
       <c r="AT139" t="n">
         <v>0</v>
       </c>
-      <c r="AU139" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV139" t="inlineStr">
         <is>
           <t>all</t>
@@ -20280,11 +18210,6 @@
       <c r="R140" t="n">
         <v>13.04921924697906</v>
       </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20297,23 +18222,13 @@
       </c>
       <c r="AP140" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR140" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS140" t="inlineStr"/>
       <c r="AT140" t="n">
         <v>0</v>
       </c>
-      <c r="AU140" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV140" t="inlineStr">
         <is>
           <t>all</t>
@@ -20421,11 +18336,6 @@
       <c r="R141" t="n">
         <v>39.41117573123709</v>
       </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20438,23 +18348,13 @@
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR141" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS141" t="inlineStr"/>
       <c r="AT141" t="n">
         <v>0</v>
       </c>
-      <c r="AU141" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV141" t="inlineStr">
         <is>
           <t>all</t>
@@ -20562,11 +18462,6 @@
       <c r="R142" t="n">
         <v>12.84708900298471</v>
       </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20579,23 +18474,13 @@
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR142" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr"/>
       <c r="AT142" t="n">
         <v>0</v>
       </c>
-      <c r="AU142" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV142" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
@@ -20712,11 +18597,6 @@
       <c r="R143" t="n">
         <v>9.912209363883965</v>
       </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20729,23 +18609,13 @@
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR143" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS143" t="inlineStr"/>
       <c r="AT143" t="n">
         <v>0</v>
       </c>
-      <c r="AU143" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV143" t="inlineStr">
         <is>
           <t>all</t>
@@ -20853,11 +18723,6 @@
       <c r="R144" t="n">
         <v>45.69827712528033</v>
       </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -20870,23 +18735,13 @@
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR144" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS144" t="inlineStr"/>
       <c r="AT144" t="n">
         <v>0</v>
       </c>
-      <c r="AU144" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV144" t="inlineStr">
         <is>
           <t>all</t>
@@ -20994,11 +18849,6 @@
       <c r="R145" t="n">
         <v>6.993927436512338</v>
       </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA145" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21011,23 +18861,13 @@
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR145" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr"/>
       <c r="AT145" t="n">
         <v>0</v>
       </c>
-      <c r="AU145" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV145" t="inlineStr">
         <is>
           <t>all</t>
@@ -21135,11 +18975,6 @@
       <c r="R146" t="n">
         <v>10.86482795915319</v>
       </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA146" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21152,23 +18987,13 @@
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR146" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr"/>
       <c r="AT146" t="n">
         <v>0</v>
       </c>
-      <c r="AU146" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV146" t="inlineStr">
         <is>
           <t>all</t>
@@ -21276,11 +19101,6 @@
       <c r="R147" t="n">
         <v>21.35065635638389</v>
       </c>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA147" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21293,23 +19113,13 @@
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR147" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS147" t="inlineStr"/>
       <c r="AT147" t="n">
         <v>0</v>
       </c>
-      <c r="AU147" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV147" t="inlineStr">
         <is>
           <t>all</t>
@@ -21417,11 +19227,6 @@
       <c r="R148" t="n">
         <v>15.68444319312903</v>
       </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21434,23 +19239,13 @@
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR148" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS148" t="inlineStr"/>
       <c r="AT148" t="n">
         <v>0</v>
       </c>
-      <c r="AU148" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV148" t="inlineStr">
         <is>
           <t>all</t>
@@ -21558,11 +19353,6 @@
       <c r="R149" t="n">
         <v>13.62128055984127</v>
       </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA149" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21575,23 +19365,13 @@
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR149" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS149" t="inlineStr"/>
       <c r="AT149" t="n">
         <v>0</v>
       </c>
-      <c r="AU149" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV149" t="inlineStr">
         <is>
           <t>all</t>
@@ -21699,11 +19479,6 @@
       <c r="R150" t="n">
         <v>19.00887851953361</v>
       </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA150" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21716,23 +19491,13 @@
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR150" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr"/>
       <c r="AT150" t="n">
         <v>0</v>
       </c>
-      <c r="AU150" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV150" t="inlineStr">
         <is>
           <t>all</t>
@@ -21840,11 +19605,6 @@
       <c r="R151" t="n">
         <v>15.35683698790919</v>
       </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21857,23 +19617,13 @@
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR151" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr"/>
       <c r="AT151" t="n">
         <v>0</v>
       </c>
-      <c r="AU151" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV151" t="inlineStr">
         <is>
           <t>all</t>
@@ -21981,11 +19731,6 @@
       <c r="R152" t="n">
         <v>9.011244410145721</v>
       </c>
-      <c r="S152" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA152" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -21998,23 +19743,13 @@
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR152" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr"/>
       <c r="AT152" t="n">
         <v>0</v>
       </c>
-      <c r="AU152" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV152" t="inlineStr">
         <is>
           <t>all</t>
@@ -22122,11 +19857,6 @@
       <c r="R153" t="n">
         <v>20.88972522346018</v>
       </c>
-      <c r="S153" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA153" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22139,23 +19869,13 @@
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR153" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr"/>
       <c r="AT153" t="n">
         <v>0</v>
       </c>
-      <c r="AU153" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV153" t="inlineStr">
         <is>
           <t>all</t>
@@ -22263,11 +19983,6 @@
       <c r="R154" t="n">
         <v>11.03072072692789</v>
       </c>
-      <c r="S154" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22280,23 +19995,13 @@
       </c>
       <c r="AP154" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR154" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr"/>
       <c r="AT154" t="n">
         <v>0</v>
       </c>
-      <c r="AU154" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV154" t="inlineStr">
         <is>
           <t>all</t>
@@ -22404,11 +20109,6 @@
       <c r="R155" t="n">
         <v>7.062701090794945</v>
       </c>
-      <c r="S155" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA155" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22421,23 +20121,13 @@
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR155" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr"/>
       <c r="AT155" t="n">
         <v>0</v>
       </c>
-      <c r="AU155" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV155" t="inlineStr">
         <is>
           <t>all</t>
@@ -22545,11 +20235,6 @@
       <c r="R156" t="n">
         <v>12.77933525529663</v>
       </c>
-      <c r="S156" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA156" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22562,23 +20247,13 @@
       </c>
       <c r="AP156" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR156" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS156" t="inlineStr"/>
       <c r="AT156" t="n">
         <v>0</v>
       </c>
-      <c r="AU156" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV156" t="inlineStr">
         <is>
           <t>all</t>
@@ -22686,11 +20361,6 @@
       <c r="R157" t="n">
         <v>29.23859168964156</v>
       </c>
-      <c r="S157" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA157" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22703,23 +20373,13 @@
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR157" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS157" t="inlineStr"/>
       <c r="AT157" t="n">
         <v>0</v>
       </c>
-      <c r="AU157" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV157" t="inlineStr">
         <is>
           <t>all</t>
@@ -22827,11 +20487,6 @@
       <c r="R158" t="n">
         <v>26.36912856447591</v>
       </c>
-      <c r="S158" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22844,23 +20499,13 @@
       </c>
       <c r="AP158" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR158" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS158" t="inlineStr"/>
       <c r="AT158" t="n">
         <v>0</v>
       </c>
-      <c r="AU158" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV158" t="inlineStr">
         <is>
           <t>all</t>
@@ -22968,11 +20613,6 @@
       <c r="R159" t="n">
         <v>24.99545336240431</v>
       </c>
-      <c r="S159" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA159" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -22985,23 +20625,13 @@
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR159" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS159" t="inlineStr"/>
       <c r="AT159" t="n">
         <v>0</v>
       </c>
-      <c r="AU159" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV159" t="inlineStr">
         <is>
           <t>all</t>
@@ -23109,11 +20739,6 @@
       <c r="R160" t="n">
         <v>8.123853373733398</v>
       </c>
-      <c r="S160" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA160" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23126,23 +20751,13 @@
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR160" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS160" t="inlineStr"/>
       <c r="AT160" t="n">
         <v>0</v>
       </c>
-      <c r="AU160" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV160" t="inlineStr">
         <is>
           <t>all</t>
@@ -23250,11 +20865,6 @@
       <c r="R161" t="n">
         <v>1.712586231619451</v>
       </c>
-      <c r="S161" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23267,23 +20877,13 @@
       </c>
       <c r="AP161" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR161" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS161" t="inlineStr"/>
       <c r="AT161" t="n">
         <v>0</v>
       </c>
-      <c r="AU161" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV161" t="inlineStr">
         <is>
           <t>all</t>
@@ -23391,11 +20991,6 @@
       <c r="R162" t="n">
         <v>26.56090805970546</v>
       </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA162" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23408,23 +21003,13 @@
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR162" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr"/>
       <c r="AT162" t="n">
         <v>0</v>
       </c>
-      <c r="AU162" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV162" t="inlineStr">
         <is>
           <t>all</t>
@@ -23532,11 +21117,6 @@
       <c r="R163" t="n">
         <v>9.275392667773644</v>
       </c>
-      <c r="S163" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA163" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23549,23 +21129,13 @@
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR163" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS163" t="inlineStr"/>
       <c r="AT163" t="n">
         <v>0</v>
       </c>
-      <c r="AU163" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV163" t="inlineStr">
         <is>
           <t>all</t>
@@ -23673,11 +21243,6 @@
       <c r="R164" t="n">
         <v>11.16933767141648</v>
       </c>
-      <c r="S164" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA164" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23690,23 +21255,13 @@
       </c>
       <c r="AP164" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR164" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS164" t="inlineStr"/>
       <c r="AT164" t="n">
         <v>0</v>
       </c>
-      <c r="AU164" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV164" t="inlineStr">
         <is>
           <t>all</t>
@@ -23814,11 +21369,6 @@
       <c r="R165" t="n">
         <v>3.071221082784363</v>
       </c>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23831,23 +21381,13 @@
       </c>
       <c r="AP165" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR165" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS165" t="inlineStr"/>
       <c r="AT165" t="n">
         <v>0</v>
       </c>
-      <c r="AU165" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV165" t="inlineStr">
         <is>
           <t>all</t>
@@ -23955,11 +21495,6 @@
       <c r="R166" t="n">
         <v>3.849504117706287</v>
       </c>
-      <c r="S166" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -23972,23 +21507,13 @@
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR166" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS166" t="inlineStr"/>
       <c r="AT166" t="n">
         <v>0</v>
       </c>
-      <c r="AU166" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV166" t="inlineStr">
         <is>
           <t>all</t>
@@ -24096,11 +21621,6 @@
       <c r="R167" t="n">
         <v>16.33976305176498</v>
       </c>
-      <c r="S167" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA167" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24113,23 +21633,13 @@
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR167" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS167" t="inlineStr"/>
       <c r="AT167" t="n">
         <v>0</v>
       </c>
-      <c r="AU167" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV167" t="inlineStr">
         <is>
           <t>all</t>
@@ -24237,11 +21747,6 @@
       <c r="R168" t="n">
         <v>9.365727388513847</v>
       </c>
-      <c r="S168" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24254,23 +21759,13 @@
       </c>
       <c r="AP168" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR168" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS168" t="inlineStr"/>
       <c r="AT168" t="n">
         <v>0</v>
       </c>
-      <c r="AU168" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV168" t="inlineStr">
         <is>
           <t>all</t>
@@ -24378,11 +21873,6 @@
       <c r="R169" t="n">
         <v>37.90741067948877</v>
       </c>
-      <c r="S169" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA169" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24395,23 +21885,13 @@
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR169" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS169" t="inlineStr"/>
       <c r="AT169" t="n">
         <v>0</v>
       </c>
-      <c r="AU169" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV169" t="inlineStr">
         <is>
           <t>all</t>
@@ -24519,11 +21999,6 @@
       <c r="R170" t="n">
         <v>14.66444792335606</v>
       </c>
-      <c r="S170" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA170" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24536,23 +22011,13 @@
       </c>
       <c r="AP170" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR170" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS170" t="inlineStr"/>
       <c r="AT170" t="n">
         <v>0</v>
       </c>
-      <c r="AU170" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV170" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
@@ -24669,11 +22134,6 @@
       <c r="R171" t="n">
         <v>8.785821936169876</v>
       </c>
-      <c r="S171" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24686,23 +22146,13 @@
       </c>
       <c r="AP171" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR171" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS171" t="inlineStr"/>
       <c r="AT171" t="n">
         <v>0</v>
       </c>
-      <c r="AU171" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV171" t="inlineStr">
         <is>
           <t>all</t>
@@ -24810,11 +22260,6 @@
       <c r="R172" t="n">
         <v>48.27501421862155</v>
       </c>
-      <c r="S172" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24827,23 +22272,13 @@
       </c>
       <c r="AP172" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR172" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS172" t="inlineStr"/>
       <c r="AT172" t="n">
         <v>0</v>
       </c>
-      <c r="AU172" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV172" t="inlineStr">
         <is>
           <t>all</t>
@@ -24951,11 +22386,6 @@
       <c r="R173" t="n">
         <v>7.406683809814704</v>
       </c>
-      <c r="S173" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA173" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -24968,23 +22398,13 @@
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR173" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS173" t="inlineStr"/>
       <c r="AT173" t="n">
         <v>0</v>
       </c>
-      <c r="AU173" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV173" t="inlineStr">
         <is>
           <t>all</t>
@@ -25092,11 +22512,6 @@
       <c r="R174" t="n">
         <v>8.642476785690034</v>
       </c>
-      <c r="S174" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA174" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25109,23 +22524,13 @@
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR174" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS174" t="inlineStr"/>
       <c r="AT174" t="n">
         <v>0</v>
       </c>
-      <c r="AU174" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV174" t="inlineStr">
         <is>
           <t>all</t>
@@ -25233,11 +22638,6 @@
       <c r="R175" t="n">
         <v>21.38423713077267</v>
       </c>
-      <c r="S175" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA175" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25250,23 +22650,13 @@
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR175" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS175" t="inlineStr"/>
       <c r="AT175" t="n">
         <v>0</v>
       </c>
-      <c r="AU175" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV175" t="inlineStr">
         <is>
           <t>all</t>
@@ -25374,11 +22764,6 @@
       <c r="R176" t="n">
         <v>15.73819385520281</v>
       </c>
-      <c r="S176" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA176" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25391,23 +22776,13 @@
       </c>
       <c r="AP176" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR176" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS176" t="inlineStr"/>
       <c r="AT176" t="n">
         <v>0</v>
       </c>
-      <c r="AU176" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV176" t="inlineStr">
         <is>
           <t>all</t>
@@ -25515,11 +22890,6 @@
       <c r="R177" t="n">
         <v>13.38872211125862</v>
       </c>
-      <c r="S177" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA177" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25532,23 +22902,13 @@
       </c>
       <c r="AP177" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR177" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS177" t="inlineStr"/>
       <c r="AT177" t="n">
         <v>0</v>
       </c>
-      <c r="AU177" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV177" t="inlineStr">
         <is>
           <t>all</t>
@@ -25656,11 +23016,6 @@
       <c r="R178" t="n">
         <v>18.38247694601286</v>
       </c>
-      <c r="S178" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA178" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25673,23 +23028,13 @@
       </c>
       <c r="AP178" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR178" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS178" t="inlineStr"/>
       <c r="AT178" t="n">
         <v>0</v>
       </c>
-      <c r="AU178" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV178" t="inlineStr">
         <is>
           <t>all</t>
@@ -25797,11 +23142,6 @@
       <c r="R179" t="n">
         <v>15.65036471487183</v>
       </c>
-      <c r="S179" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA179" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25814,23 +23154,13 @@
       </c>
       <c r="AP179" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR179" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS179" t="inlineStr"/>
       <c r="AT179" t="n">
         <v>0</v>
       </c>
-      <c r="AU179" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV179" t="inlineStr">
         <is>
           <t>all</t>
@@ -25938,11 +23268,6 @@
       <c r="R180" t="n">
         <v>9.908098119212356</v>
       </c>
-      <c r="S180" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA180" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -25955,23 +23280,13 @@
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR180" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS180" t="inlineStr"/>
       <c r="AT180" t="n">
         <v>0</v>
       </c>
-      <c r="AU180" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV180" t="inlineStr">
         <is>
           <t>all</t>
@@ -26079,11 +23394,6 @@
       <c r="R181" t="n">
         <v>23.18232946391131</v>
       </c>
-      <c r="S181" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA181" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26096,23 +23406,13 @@
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR181" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS181" t="inlineStr"/>
       <c r="AT181" t="n">
         <v>0</v>
       </c>
-      <c r="AU181" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV181" t="inlineStr">
         <is>
           <t>all</t>
@@ -26220,11 +23520,6 @@
       <c r="R182" t="n">
         <v>10.01250035213455</v>
       </c>
-      <c r="S182" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA182" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26237,23 +23532,13 @@
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR182" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS182" t="inlineStr"/>
       <c r="AT182" t="n">
         <v>0</v>
       </c>
-      <c r="AU182" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV182" t="inlineStr">
         <is>
           <t>all</t>
@@ -26361,11 +23646,6 @@
       <c r="R183" t="n">
         <v>7.442416203203276</v>
       </c>
-      <c r="S183" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA183" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26378,23 +23658,13 @@
       </c>
       <c r="AP183" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR183" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS183" t="inlineStr"/>
       <c r="AT183" t="n">
         <v>0</v>
       </c>
-      <c r="AU183" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV183" t="inlineStr">
         <is>
           <t>all</t>
@@ -26502,11 +23772,6 @@
       <c r="R184" t="n">
         <v>13.56733716111921</v>
       </c>
-      <c r="S184" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA184" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26519,23 +23784,13 @@
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR184" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS184" t="inlineStr"/>
       <c r="AT184" t="n">
         <v>0</v>
       </c>
-      <c r="AU184" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV184" t="inlineStr">
         <is>
           <t>all</t>
@@ -26643,11 +23898,6 @@
       <c r="R185" t="n">
         <v>30.14706796454456</v>
       </c>
-      <c r="S185" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA185" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26660,23 +23910,13 @@
       </c>
       <c r="AP185" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR185" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS185" t="inlineStr"/>
       <c r="AT185" t="n">
         <v>0</v>
       </c>
-      <c r="AU185" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV185" t="inlineStr">
         <is>
           <t>all</t>
@@ -26784,11 +24024,6 @@
       <c r="R186" t="n">
         <v>27.94480660691195</v>
       </c>
-      <c r="S186" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA186" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26801,23 +24036,13 @@
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR186" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS186" t="inlineStr"/>
       <c r="AT186" t="n">
         <v>0</v>
       </c>
-      <c r="AU186" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV186" t="inlineStr">
         <is>
           <t>all</t>
@@ -26925,11 +24150,6 @@
       <c r="R187" t="n">
         <v>27.47141808226511</v>
       </c>
-      <c r="S187" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA187" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -26942,23 +24162,13 @@
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR187" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS187" t="inlineStr"/>
       <c r="AT187" t="n">
         <v>0</v>
       </c>
-      <c r="AU187" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV187" t="inlineStr">
         <is>
           <t>all</t>
@@ -27066,11 +24276,6 @@
       <c r="R188" t="n">
         <v>10.2907720388178</v>
       </c>
-      <c r="S188" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA188" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27083,23 +24288,13 @@
       </c>
       <c r="AP188" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR188" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS188" t="inlineStr"/>
       <c r="AT188" t="n">
         <v>0</v>
       </c>
-      <c r="AU188" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV188" t="inlineStr">
         <is>
           <t>all</t>
@@ -27207,11 +24402,6 @@
       <c r="R189" t="n">
         <v>2.002855084436307</v>
       </c>
-      <c r="S189" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA189" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27224,23 +24414,13 @@
       </c>
       <c r="AP189" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR189" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS189" t="inlineStr"/>
       <c r="AT189" t="n">
         <v>0</v>
       </c>
-      <c r="AU189" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV189" t="inlineStr">
         <is>
           <t>all</t>
@@ -27348,11 +24528,6 @@
       <c r="R190" t="n">
         <v>27.36928352239214</v>
       </c>
-      <c r="S190" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA190" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27365,23 +24540,13 @@
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR190" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS190" t="inlineStr"/>
       <c r="AT190" t="n">
         <v>0</v>
       </c>
-      <c r="AU190" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV190" t="inlineStr">
         <is>
           <t>all</t>
@@ -27489,11 +24654,6 @@
       <c r="R191" t="n">
         <v>7.113031186942978</v>
       </c>
-      <c r="S191" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA191" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27506,23 +24666,13 @@
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR191" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS191" t="inlineStr"/>
       <c r="AT191" t="n">
         <v>0</v>
       </c>
-      <c r="AU191" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV191" t="inlineStr">
         <is>
           <t>all</t>
@@ -27630,11 +24780,6 @@
       <c r="R192" t="n">
         <v>12.08916547965078</v>
       </c>
-      <c r="S192" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA192" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27647,23 +24792,13 @@
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR192" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS192" t="inlineStr"/>
       <c r="AT192" t="n">
         <v>0</v>
       </c>
-      <c r="AU192" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV192" t="inlineStr">
         <is>
           <t>all</t>
@@ -27771,11 +24906,6 @@
       <c r="R193" t="n">
         <v>3.498521407345667</v>
       </c>
-      <c r="S193" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA193" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27788,23 +24918,13 @@
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR193" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS193" t="inlineStr"/>
       <c r="AT193" t="n">
         <v>0</v>
       </c>
-      <c r="AU193" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV193" t="inlineStr">
         <is>
           <t>all</t>
@@ -27912,11 +25032,6 @@
       <c r="R194" t="n">
         <v>4.378810933890902</v>
       </c>
-      <c r="S194" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA194" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -27929,23 +25044,13 @@
       </c>
       <c r="AP194" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR194" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS194" t="inlineStr"/>
       <c r="AT194" t="n">
         <v>0</v>
       </c>
-      <c r="AU194" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV194" t="inlineStr">
         <is>
           <t>all</t>
@@ -28053,11 +25158,6 @@
       <c r="R195" t="n">
         <v>16.33976305176498</v>
       </c>
-      <c r="S195" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA195" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28070,23 +25170,13 @@
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR195" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS195" t="inlineStr"/>
       <c r="AT195" t="n">
         <v>0</v>
       </c>
-      <c r="AU195" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV195" t="inlineStr">
         <is>
           <t>all</t>
@@ -28194,11 +25284,6 @@
       <c r="R196" t="n">
         <v>11.94265584916852</v>
       </c>
-      <c r="S196" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA196" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28211,23 +25296,13 @@
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR196" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS196" t="inlineStr"/>
       <c r="AT196" t="n">
         <v>0</v>
       </c>
-      <c r="AU196" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV196" t="inlineStr">
         <is>
           <t>all</t>
@@ -28335,11 +25410,6 @@
       <c r="R197" t="n">
         <v>42.54401958904607</v>
       </c>
-      <c r="S197" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA197" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28352,23 +25422,13 @@
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR197" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS197" t="inlineStr"/>
       <c r="AT197" t="n">
         <v>0</v>
       </c>
-      <c r="AU197" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV197" t="inlineStr">
         <is>
           <t>all</t>
@@ -28476,11 +25536,6 @@
       <c r="R198" t="n">
         <v>13.92265924509506</v>
       </c>
-      <c r="S198" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA198" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28493,23 +25548,13 @@
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR198" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS198" t="inlineStr"/>
       <c r="AT198" t="n">
         <v>0</v>
       </c>
-      <c r="AU198" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV198" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
@@ -28626,11 +25671,6 @@
       <c r="R199" t="n">
         <v>10.58804182051242</v>
       </c>
-      <c r="S199" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA199" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28643,23 +25683,13 @@
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR199" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS199" t="inlineStr"/>
       <c r="AT199" t="n">
         <v>0</v>
       </c>
-      <c r="AU199" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV199" t="inlineStr">
         <is>
           <t>all</t>
@@ -28767,11 +25797,6 @@
       <c r="R200" t="n">
         <v>37.31612031561615</v>
       </c>
-      <c r="S200" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA200" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28784,23 +25809,13 @@
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR200" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS200" t="inlineStr"/>
       <c r="AT200" t="n">
         <v>0</v>
       </c>
-      <c r="AU200" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV200" t="inlineStr">
         <is>
           <t>all</t>
@@ -28908,11 +25923,6 @@
       <c r="R201" t="n">
         <v>7.429614719442615</v>
       </c>
-      <c r="S201" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA201" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -28925,23 +25935,13 @@
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR201" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS201" t="inlineStr"/>
       <c r="AT201" t="n">
         <v>0</v>
       </c>
-      <c r="AU201" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV201" t="inlineStr">
         <is>
           <t>all</t>
@@ -29049,11 +26049,6 @@
       <c r="R202" t="n">
         <v>8.14862096936489</v>
       </c>
-      <c r="S202" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA202" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29066,23 +26061,13 @@
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR202" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS202" t="inlineStr"/>
       <c r="AT202" t="n">
         <v>0</v>
       </c>
-      <c r="AU202" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV202" t="inlineStr">
         <is>
           <t>all</t>
@@ -29190,11 +26175,6 @@
       <c r="R203" t="n">
         <v>18.65747825040404</v>
       </c>
-      <c r="S203" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA203" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29207,23 +26187,13 @@
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR203" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS203" t="inlineStr"/>
       <c r="AT203" t="n">
         <v>0</v>
       </c>
-      <c r="AU203" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV203" t="inlineStr">
         <is>
           <t>all</t>
@@ -29331,11 +26301,6 @@
       <c r="R204" t="n">
         <v>11.1693875789315</v>
       </c>
-      <c r="S204" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA204" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29348,23 +26313,13 @@
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR204" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS204" t="inlineStr"/>
       <c r="AT204" t="n">
         <v>0</v>
       </c>
-      <c r="AU204" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV204" t="inlineStr">
         <is>
           <t>all</t>
@@ -29472,11 +26427,6 @@
       <c r="R205" t="n">
         <v>14.11962009251839</v>
       </c>
-      <c r="S205" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA205" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29489,23 +26439,13 @@
       </c>
       <c r="AP205" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR205" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS205" t="inlineStr"/>
       <c r="AT205" t="n">
         <v>0</v>
       </c>
-      <c r="AU205" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV205" t="inlineStr">
         <is>
           <t>all</t>
@@ -29613,11 +26553,6 @@
       <c r="R206" t="n">
         <v>15.63594696980648</v>
       </c>
-      <c r="S206" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA206" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29630,23 +26565,13 @@
       </c>
       <c r="AP206" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR206" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS206" t="inlineStr"/>
       <c r="AT206" t="n">
         <v>0</v>
       </c>
-      <c r="AU206" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV206" t="inlineStr">
         <is>
           <t>all</t>
@@ -29754,11 +26679,6 @@
       <c r="R207" t="n">
         <v>15.11667793857612</v>
       </c>
-      <c r="S207" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA207" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29771,23 +26691,13 @@
       </c>
       <c r="AP207" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR207" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS207" t="inlineStr"/>
       <c r="AT207" t="n">
         <v>0</v>
       </c>
-      <c r="AU207" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV207" t="inlineStr">
         <is>
           <t>all</t>
@@ -29895,11 +26805,6 @@
       <c r="R208" t="n">
         <v>7.872382557362692</v>
       </c>
-      <c r="S208" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA208" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -29912,23 +26817,13 @@
       </c>
       <c r="AP208" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR208" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS208" t="inlineStr"/>
       <c r="AT208" t="n">
         <v>0</v>
       </c>
-      <c r="AU208" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV208" t="inlineStr">
         <is>
           <t>all</t>
@@ -30036,11 +26931,6 @@
       <c r="R209" t="n">
         <v>23.43395675859497</v>
       </c>
-      <c r="S209" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA209" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30053,23 +26943,13 @@
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR209" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS209" t="inlineStr"/>
       <c r="AT209" t="n">
         <v>0</v>
       </c>
-      <c r="AU209" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV209" t="inlineStr">
         <is>
           <t>all</t>
@@ -30177,11 +27057,6 @@
       <c r="R210" t="n">
         <v>4.412288290771156</v>
       </c>
-      <c r="S210" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA210" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30194,23 +27069,13 @@
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR210" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS210" t="inlineStr"/>
       <c r="AT210" t="n">
         <v>0</v>
       </c>
-      <c r="AU210" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV210" t="inlineStr">
         <is>
           <t>all</t>
@@ -30318,11 +27183,6 @@
       <c r="R211" t="n">
         <v>5.240068551234961</v>
       </c>
-      <c r="S211" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA211" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30335,23 +27195,13 @@
       </c>
       <c r="AP211" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR211" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS211" t="inlineStr"/>
       <c r="AT211" t="n">
         <v>0</v>
       </c>
-      <c r="AU211" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV211" t="inlineStr">
         <is>
           <t>all</t>
@@ -30459,11 +27309,6 @@
       <c r="R212" t="n">
         <v>9.57022604462786</v>
       </c>
-      <c r="S212" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA212" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30476,23 +27321,13 @@
       </c>
       <c r="AP212" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR212" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS212" t="inlineStr"/>
       <c r="AT212" t="n">
         <v>0</v>
       </c>
-      <c r="AU212" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV212" t="inlineStr">
         <is>
           <t>all</t>
@@ -30600,11 +27435,6 @@
       <c r="R213" t="n">
         <v>26.15455380904976</v>
       </c>
-      <c r="S213" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA213" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30617,23 +27447,13 @@
       </c>
       <c r="AP213" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR213" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS213" t="inlineStr"/>
       <c r="AT213" t="n">
         <v>0</v>
       </c>
-      <c r="AU213" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV213" t="inlineStr">
         <is>
           <t>all</t>
@@ -30741,11 +27561,6 @@
       <c r="R214" t="n">
         <v>23.00907340113549</v>
       </c>
-      <c r="S214" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA214" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30758,23 +27573,13 @@
       </c>
       <c r="AP214" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR214" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS214" t="inlineStr"/>
       <c r="AT214" t="n">
         <v>0</v>
       </c>
-      <c r="AU214" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV214" t="inlineStr">
         <is>
           <t>all</t>
@@ -30882,11 +27687,6 @@
       <c r="R215" t="n">
         <v>21.78259438068016</v>
       </c>
-      <c r="S215" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA215" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -30899,23 +27699,13 @@
       </c>
       <c r="AP215" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR215" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS215" t="inlineStr"/>
       <c r="AT215" t="n">
         <v>0</v>
       </c>
-      <c r="AU215" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV215" t="inlineStr">
         <is>
           <t>all</t>
@@ -31023,11 +27813,6 @@
       <c r="R216" t="n">
         <v>12.77561699453234</v>
       </c>
-      <c r="S216" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA216" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31040,23 +27825,13 @@
       </c>
       <c r="AP216" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR216" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS216" t="inlineStr"/>
       <c r="AT216" t="n">
         <v>0</v>
       </c>
-      <c r="AU216" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV216" t="inlineStr">
         <is>
           <t>all</t>
@@ -31164,11 +27939,6 @@
       <c r="R217" t="n">
         <v>1.335236722957538</v>
       </c>
-      <c r="S217" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA217" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31181,23 +27951,13 @@
       </c>
       <c r="AP217" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR217" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS217" t="inlineStr"/>
       <c r="AT217" t="n">
         <v>0</v>
       </c>
-      <c r="AU217" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV217" t="inlineStr">
         <is>
           <t>all</t>
@@ -31305,11 +28065,6 @@
       <c r="R218" t="n">
         <v>28.72619947761623</v>
       </c>
-      <c r="S218" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA218" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31322,23 +28077,13 @@
       </c>
       <c r="AP218" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR218" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS218" t="inlineStr"/>
       <c r="AT218" t="n">
         <v>0</v>
       </c>
-      <c r="AU218" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV218" t="inlineStr">
         <is>
           <t>all</t>
@@ -31446,11 +28191,6 @@
       <c r="R219" t="n">
         <v>4.324722961661331</v>
       </c>
-      <c r="S219" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA219" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31463,23 +28203,13 @@
       </c>
       <c r="AP219" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR219" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS219" t="inlineStr"/>
       <c r="AT219" t="n">
         <v>0</v>
       </c>
-      <c r="AU219" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV219" t="inlineStr">
         <is>
           <t>all</t>
@@ -31587,11 +28317,6 @@
       <c r="R220" t="n">
         <v>13.66601315090958</v>
       </c>
-      <c r="S220" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA220" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31604,23 +28329,13 @@
       </c>
       <c r="AP220" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR220" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS220" t="inlineStr"/>
       <c r="AT220" t="n">
         <v>0</v>
       </c>
-      <c r="AU220" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV220" t="inlineStr">
         <is>
           <t>all</t>
@@ -31728,11 +28443,6 @@
       <c r="R221" t="n">
         <v>4.370926236658327</v>
       </c>
-      <c r="S221" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA221" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31745,23 +28455,13 @@
       </c>
       <c r="AP221" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR221" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS221" t="inlineStr"/>
       <c r="AT221" t="n">
         <v>0</v>
       </c>
-      <c r="AU221" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV221" t="inlineStr">
         <is>
           <t>all</t>
@@ -31869,11 +28569,6 @@
       <c r="R222" t="n">
         <v>6.568216400836353</v>
       </c>
-      <c r="S222" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA222" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -31886,23 +28581,13 @@
       </c>
       <c r="AP222" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR222" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS222" t="inlineStr"/>
       <c r="AT222" t="n">
         <v>0</v>
       </c>
-      <c r="AU222" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV222" t="inlineStr">
         <is>
           <t>all</t>
@@ -32010,11 +28695,6 @@
       <c r="R223" t="n">
         <v>15.64629830686248</v>
       </c>
-      <c r="S223" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA223" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32027,23 +28707,13 @@
       </c>
       <c r="AP223" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR223" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS223" t="inlineStr"/>
       <c r="AT223" t="n">
         <v>0</v>
       </c>
-      <c r="AU223" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV223" t="inlineStr">
         <is>
           <t>all</t>
@@ -32151,11 +28821,6 @@
       <c r="R224" t="n">
         <v>13.86777299330466</v>
       </c>
-      <c r="S224" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA224" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32168,23 +28833,13 @@
       </c>
       <c r="AP224" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR224" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS224" t="inlineStr"/>
       <c r="AT224" t="n">
         <v>0</v>
       </c>
-      <c r="AU224" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV224" t="inlineStr">
         <is>
           <t>all</t>
@@ -32292,11 +28947,6 @@
       <c r="R225" t="n">
         <v>35.83973373333484</v>
       </c>
-      <c r="S225" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA225" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32309,23 +28959,13 @@
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR225" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS225" t="inlineStr"/>
       <c r="AT225" t="n">
         <v>0</v>
       </c>
-      <c r="AU225" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV225" t="inlineStr">
         <is>
           <t>all</t>
@@ -32433,11 +29073,6 @@
       <c r="R226" t="n">
         <v>0.5051072057132797</v>
       </c>
-      <c r="S226" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA226" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32450,23 +29085,13 @@
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR226" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS226" t="inlineStr"/>
       <c r="AT226" t="n">
         <v>0</v>
       </c>
-      <c r="AU226" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV226" t="inlineStr">
         <is>
           <t>sinan_datasus</t>
@@ -32583,11 +29208,6 @@
       <c r="R227" t="n">
         <v>0.1126387427714087</v>
       </c>
-      <c r="S227" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA227" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32600,23 +29220,13 @@
       </c>
       <c r="AP227" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR227" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS227" t="inlineStr"/>
       <c r="AT227" t="n">
         <v>0</v>
       </c>
-      <c r="AU227" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV227" t="inlineStr">
         <is>
           <t>all</t>
@@ -32724,11 +29334,6 @@
       <c r="R228" t="n">
         <v>1.24180100883914</v>
       </c>
-      <c r="S228" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA228" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32741,23 +29346,13 @@
       </c>
       <c r="AP228" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR228" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS228" t="inlineStr"/>
       <c r="AT228" t="n">
         <v>0</v>
       </c>
-      <c r="AU228" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV228" t="inlineStr">
         <is>
           <t>all</t>
@@ -32865,11 +29460,6 @@
       <c r="R229" t="n">
         <v>0.06879272888372791</v>
       </c>
-      <c r="S229" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA229" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -32882,23 +29472,13 @@
       </c>
       <c r="AP229" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR229" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS229" t="inlineStr"/>
       <c r="AT229" t="n">
         <v>0</v>
       </c>
-      <c r="AU229" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV229" t="inlineStr">
         <is>
           <t>all</t>
@@ -33006,11 +29586,6 @@
       <c r="R230" t="n">
         <v>0</v>
       </c>
-      <c r="S230" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA230" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33023,23 +29598,13 @@
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR230" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS230" t="inlineStr"/>
       <c r="AT230" t="n">
         <v>0</v>
       </c>
-      <c r="AU230" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV230" t="inlineStr">
         <is>
           <t>all</t>
@@ -33147,11 +29712,6 @@
       <c r="R231" t="n">
         <v>0.3223754341322513</v>
       </c>
-      <c r="S231" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA231" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33164,23 +29724,13 @@
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR231" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS231" t="inlineStr"/>
       <c r="AT231" t="n">
         <v>0</v>
       </c>
-      <c r="AU231" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV231" t="inlineStr">
         <is>
           <t>all</t>
@@ -33288,11 +29838,6 @@
       <c r="R232" t="n">
         <v>0.1935023834656083</v>
       </c>
-      <c r="S232" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA232" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33305,23 +29850,13 @@
       </c>
       <c r="AP232" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR232" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS232" t="inlineStr"/>
       <c r="AT232" t="n">
         <v>0</v>
       </c>
-      <c r="AU232" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV232" t="inlineStr">
         <is>
           <t>all</t>
@@ -33429,11 +29964,6 @@
       <c r="R233" t="n">
         <v>0.6976753457479679</v>
       </c>
-      <c r="S233" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA233" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33446,23 +29976,13 @@
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR233" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS233" t="inlineStr"/>
       <c r="AT233" t="n">
         <v>0</v>
       </c>
-      <c r="AU233" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV233" t="inlineStr">
         <is>
           <t>all</t>
@@ -33570,11 +30090,6 @@
       <c r="R234" t="n">
         <v>12.26301542007935</v>
       </c>
-      <c r="S234" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA234" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33587,23 +30102,13 @@
       </c>
       <c r="AP234" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR234" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS234" t="inlineStr"/>
       <c r="AT234" t="n">
         <v>0</v>
       </c>
-      <c r="AU234" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV234" t="inlineStr">
         <is>
           <t>all</t>
@@ -33711,11 +30216,6 @@
       <c r="R235" t="n">
         <v>0.4269494210365718</v>
       </c>
-      <c r="S235" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA235" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33728,23 +30228,13 @@
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR235" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS235" t="inlineStr"/>
       <c r="AT235" t="n">
         <v>0</v>
       </c>
-      <c r="AU235" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV235" t="inlineStr">
         <is>
           <t>all</t>
@@ -33852,11 +30342,6 @@
       <c r="R236" t="n">
         <v>0.1423577315978787</v>
       </c>
-      <c r="S236" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA236" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -33869,23 +30354,13 @@
       </c>
       <c r="AP236" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR236" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS236" t="inlineStr"/>
       <c r="AT236" t="n">
         <v>0</v>
       </c>
-      <c r="AU236" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV236" t="inlineStr">
         <is>
           <t>all</t>
@@ -33993,11 +30468,6 @@
       <c r="R237" t="n">
         <v>0.6150889425600589</v>
       </c>
-      <c r="S237" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA237" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -34010,23 +30480,13 @@
       </c>
       <c r="AP237" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR237" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS237" t="inlineStr"/>
       <c r="AT237" t="n">
         <v>0</v>
       </c>
-      <c r="AU237" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV237" t="inlineStr">
         <is>
           <t>all</t>
@@ -34134,11 +30594,6 @@
       <c r="R238" t="n">
         <v>0.2375847541184469</v>
       </c>
-      <c r="S238" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA238" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -34151,23 +30606,13 @@
       </c>
       <c r="AP238" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR238" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS238" t="inlineStr"/>
       <c r="AT238" t="n">
         <v>0</v>
       </c>
-      <c r="AU238" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV238" t="inlineStr">
         <is>
           <t>all</t>
@@ -34275,11 +30720,6 @@
       <c r="R239" t="n">
         <v>0</v>
       </c>
-      <c r="S239" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA239" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -34292,23 +30732,13 @@
       </c>
       <c r="AP239" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR239" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS239" t="inlineStr"/>
       <c r="AT239" t="n">
         <v>0</v>
       </c>
-      <c r="AU239" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV239" t="inlineStr">
         <is>
           <t>all</t>
@@ -34416,11 +30846,6 @@
       <c r="R240" t="n">
         <v>0.09136253980551656</v>
       </c>
-      <c r="S240" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA240" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -34433,23 +30858,13 @@
       </c>
       <c r="AP240" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR240" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS240" t="inlineStr"/>
       <c r="AT240" t="n">
         <v>0</v>
       </c>
-      <c r="AU240" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV240" t="inlineStr">
         <is>
           <t>all</t>
@@ -34557,11 +30972,6 @@
       <c r="R241" t="n">
         <v>0.3825163262749508</v>
       </c>
-      <c r="S241" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA241" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -34574,23 +30984,13 @@
       </c>
       <c r="AP241" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR241" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS241" t="inlineStr"/>
       <c r="AT241" t="n">
         <v>0</v>
       </c>
-      <c r="AU241" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV241" t="inlineStr">
         <is>
           <t>all</t>
@@ -34698,11 +31098,6 @@
       <c r="R242" t="n">
         <v>0.2608738480854364</v>
       </c>
-      <c r="S242" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA242" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -34715,23 +31110,13 @@
       </c>
       <c r="AP242" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR242" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS242" t="inlineStr"/>
       <c r="AT242" t="n">
         <v>0</v>
       </c>
-      <c r="AU242" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV242" t="inlineStr">
         <is>
           <t>all</t>
@@ -34839,11 +31224,6 @@
       <c r="R243" t="n">
         <v>0.4421365571180007</v>
       </c>
-      <c r="S243" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA243" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -34856,23 +31236,13 @@
       </c>
       <c r="AP243" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR243" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS243" t="inlineStr"/>
       <c r="AT243" t="n">
         <v>0</v>
       </c>
-      <c r="AU243" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV243" t="inlineStr">
         <is>
           <t>all</t>
@@ -34980,11 +31350,6 @@
       <c r="R244" t="n">
         <v>0.3179262906301433</v>
       </c>
-      <c r="S244" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA244" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -34997,23 +31362,13 @@
       </c>
       <c r="AP244" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR244" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS244" t="inlineStr"/>
       <c r="AT244" t="n">
         <v>0</v>
       </c>
-      <c r="AU244" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV244" t="inlineStr">
         <is>
           <t>all</t>
@@ -35121,11 +31476,6 @@
       <c r="R245" t="n">
         <v>0.01741613116901136</v>
       </c>
-      <c r="S245" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA245" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35138,23 +31488,13 @@
       </c>
       <c r="AP245" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR245" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS245" t="inlineStr"/>
       <c r="AT245" t="n">
         <v>0</v>
       </c>
-      <c r="AU245" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV245" t="inlineStr">
         <is>
           <t>all</t>
@@ -35262,11 +31602,6 @@
       <c r="R246" t="n">
         <v>0.4907993880597748</v>
       </c>
-      <c r="S246" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA246" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35279,23 +31614,13 @@
       </c>
       <c r="AP246" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR246" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS246" t="inlineStr"/>
       <c r="AT246" t="n">
         <v>0</v>
       </c>
-      <c r="AU246" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV246" t="inlineStr">
         <is>
           <t>all</t>
@@ -35403,11 +31728,6 @@
       <c r="R247" t="n">
         <v>0.05690424949554383</v>
       </c>
-      <c r="S247" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA247" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35420,23 +31740,13 @@
       </c>
       <c r="AP247" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR247" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS247" t="inlineStr"/>
       <c r="AT247" t="n">
         <v>0</v>
       </c>
-      <c r="AU247" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV247" t="inlineStr">
         <is>
           <t>all</t>
@@ -35544,11 +31854,6 @@
       <c r="R248" t="n">
         <v>0.1314039726048998</v>
       </c>
-      <c r="S248" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA248" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35561,23 +31866,13 @@
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR248" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS248" t="inlineStr"/>
       <c r="AT248" t="n">
         <v>0</v>
       </c>
-      <c r="AU248" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV248" t="inlineStr">
         <is>
           <t>all</t>
@@ -35685,11 +31980,6 @@
       <c r="R249" t="n">
         <v>0.06231463066518999</v>
       </c>
-      <c r="S249" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA249" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35702,23 +31992,13 @@
       </c>
       <c r="AP249" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR249" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS249" t="inlineStr"/>
       <c r="AT249" t="n">
         <v>0</v>
       </c>
-      <c r="AU249" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV249" t="inlineStr">
         <is>
           <t>all</t>
@@ -35826,11 +32106,6 @@
       <c r="R250" t="n">
         <v>0.2045049062531465</v>
       </c>
-      <c r="S250" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA250" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35843,23 +32118,13 @@
       </c>
       <c r="AP250" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR250" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS250" t="inlineStr"/>
       <c r="AT250" t="n">
         <v>0</v>
       </c>
-      <c r="AU250" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV250" t="inlineStr">
         <is>
           <t>all</t>
@@ -35967,11 +32232,6 @@
       <c r="R251" t="n">
         <v>0.3900739190076519</v>
       </c>
-      <c r="S251" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA251" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -35984,23 +32244,13 @@
       </c>
       <c r="AP251" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR251" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS251" t="inlineStr"/>
       <c r="AT251" t="n">
         <v>0</v>
       </c>
-      <c r="AU251" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV251" t="inlineStr">
         <is>
           <t>all</t>
@@ -36108,11 +32358,6 @@
       <c r="R252" t="n">
         <v>0.1840663186181912</v>
       </c>
-      <c r="S252" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA252" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -36125,23 +32370,13 @@
       </c>
       <c r="AP252" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR252" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS252" t="inlineStr"/>
       <c r="AT252" t="n">
         <v>0</v>
       </c>
-      <c r="AU252" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV252" t="inlineStr">
         <is>
           <t>all</t>
@@ -36249,11 +32484,6 @@
       <c r="R253" t="n">
         <v>1.190480665967416</v>
       </c>
-      <c r="S253" t="inlineStr">
-        <is>
-          <t>ibge_computed</t>
-        </is>
-      </c>
       <c r="AA253" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -36266,22 +32496,12 @@
       </c>
       <c r="AP253" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR253" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS253" t="inlineStr"/>
       <c r="AT253" t="n">
         <v>0</v>
-      </c>
-      <c r="AU253" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV253" t="inlineStr">
         <is>
